--- a/memo/フリガナチェック.xlsx
+++ b/memo/フリガナチェック.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saisen-my.sharepoint.com/personal/ochi_saisen_ac_jp/Documents/ドキュメント/MyDocs/JavaScript_new/memo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{523B395E-461C-49F3-9826-BD1CEC3361E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{523B395E-461C-49F3-9826-BD1CEC3361E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C0FB26D-5484-43DE-BAEB-976349BEBBAA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8071D02F-48A5-4AAB-9F2F-C41812D8E7C4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="615">
   <si>
     <t>－－</t>
   </si>
@@ -1893,6 +1893,125 @@
   </si>
   <si>
     <t>操れる</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>N1 10 (7)</t>
+  </si>
+  <si>
+    <t>アップ</t>
+  </si>
+  <si>
+    <t>中級</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一歩</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>くみこむ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>黄</t>
+  </si>
+  <si>
+    <t>いちご</t>
+  </si>
+  <si>
+    <t>入れかえる</t>
+  </si>
+  <si>
+    <t>チョコ</t>
+  </si>
+  <si>
+    <t>グミ</t>
+  </si>
+  <si>
+    <t>アイス</t>
+  </si>
+  <si>
+    <t>住人</t>
+  </si>
+  <si>
+    <t>レングス</t>
+  </si>
+  <si>
+    <t>ジョン</t>
+  </si>
+  <si>
+    <t>リー</t>
+  </si>
+  <si>
+    <t>リーダー</t>
+  </si>
+  <si>
+    <t>プッシュ</t>
+  </si>
+  <si>
+    <t>おしり</t>
+  </si>
+  <si>
+    <t>れん</t>
+  </si>
+  <si>
+    <t>ポップ</t>
+  </si>
+  <si>
+    <t>シフト</t>
+  </si>
+  <si>
+    <t>スライス</t>
+  </si>
+  <si>
+    <t>N1 53 (12)</t>
+  </si>
+  <si>
+    <t>けつ</t>
+  </si>
+  <si>
+    <t>配</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>号室</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>唱</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>書き直す</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>車両</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>連結</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>離</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>切り取る</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>柔軟</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対応</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>取り除く</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -6655,201 +6774,271 @@
       <c r="A582" s="6"/>
       <c r="B582" s="4"/>
       <c r="C582" s="5"/>
-      <c r="D582"/>
+      <c r="D582" s="6" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A583" s="6"/>
       <c r="B583" s="4"/>
       <c r="C583" s="5"/>
-      <c r="D583"/>
+      <c r="D583" s="6" t="s">
+        <v>583</v>
+      </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A584" s="6"/>
       <c r="B584" s="6"/>
       <c r="C584" s="5"/>
-      <c r="D584"/>
+      <c r="D584" s="6" t="s">
+        <v>580</v>
+      </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A585" s="6"/>
       <c r="B585" s="4"/>
       <c r="C585" s="5"/>
-      <c r="D585"/>
+      <c r="D585" s="6" t="s">
+        <v>584</v>
+      </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A586" s="6"/>
       <c r="B586" s="4"/>
       <c r="C586" s="5"/>
-      <c r="D586"/>
+      <c r="D586" s="6" t="s">
+        <v>581</v>
+      </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A587" s="6"/>
       <c r="B587" s="4"/>
       <c r="C587" s="5"/>
-      <c r="D587"/>
+      <c r="D587" s="6" t="s">
+        <v>604</v>
+      </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A588" s="6"/>
       <c r="B588" s="4"/>
       <c r="C588" s="5"/>
-      <c r="D588"/>
+      <c r="D588" s="6" t="s">
+        <v>585</v>
+      </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A589" s="6"/>
       <c r="B589" s="4"/>
       <c r="C589" s="5"/>
-      <c r="D589"/>
+      <c r="D589" s="6" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A590" s="6"/>
       <c r="B590" s="4"/>
       <c r="C590" s="5"/>
-      <c r="D590"/>
+      <c r="D590" s="6" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A591" s="6"/>
       <c r="B591" s="4"/>
       <c r="C591" s="5"/>
-      <c r="D591"/>
+      <c r="D591" s="6" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A592" s="6"/>
       <c r="B592" s="4"/>
       <c r="C592" s="5"/>
-      <c r="D592"/>
+      <c r="D592" s="6" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B593" s="2"/>
-      <c r="D593"/>
+      <c r="D593" s="6" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A594" s="6"/>
       <c r="B594" s="4"/>
       <c r="C594" s="5"/>
-      <c r="D594"/>
+      <c r="D594" s="6" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A595" s="6"/>
       <c r="B595" s="4"/>
       <c r="C595" s="5"/>
-      <c r="D595"/>
+      <c r="D595" s="6" t="s">
+        <v>590</v>
+      </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A596" s="6"/>
       <c r="B596" s="4"/>
       <c r="C596" s="5"/>
-      <c r="D596"/>
+      <c r="D596" s="6" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B597" s="1"/>
-      <c r="D597"/>
+      <c r="D597" s="6" t="s">
+        <v>592</v>
+      </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A598" s="6"/>
       <c r="B598" s="4"/>
       <c r="C598" s="5"/>
-      <c r="D598"/>
+      <c r="D598" s="6" t="s">
+        <v>593</v>
+      </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A599" s="6"/>
       <c r="B599" s="4"/>
       <c r="C599" s="5"/>
-      <c r="D599"/>
+      <c r="D599" s="6" t="s">
+        <v>594</v>
+      </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A600" s="6"/>
       <c r="B600" s="4"/>
       <c r="C600" s="5"/>
-      <c r="D600"/>
+      <c r="D600" s="6" t="s">
+        <v>595</v>
+      </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A601" s="6"/>
       <c r="B601" s="4"/>
       <c r="C601" s="5"/>
-      <c r="D601"/>
+      <c r="D601" s="6" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A602" s="6"/>
       <c r="B602" s="4"/>
       <c r="C602" s="5"/>
-      <c r="D602"/>
+      <c r="D602" s="6" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B603" s="1"/>
-      <c r="D603"/>
+      <c r="D603" s="6" t="s">
+        <v>596</v>
+      </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B604" s="2"/>
-      <c r="D604"/>
+      <c r="D604" s="6" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A605" s="6"/>
       <c r="B605" s="4"/>
       <c r="C605" s="5"/>
-      <c r="D605"/>
+      <c r="D605" s="6" t="s">
+        <v>609</v>
+      </c>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A606" s="6"/>
       <c r="B606" s="8"/>
       <c r="C606" s="5"/>
-      <c r="D606"/>
+      <c r="D606" s="6" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A607" s="6"/>
       <c r="B607" s="4"/>
       <c r="C607" s="5"/>
-      <c r="D607"/>
+      <c r="D607" s="6" t="s">
+        <v>599</v>
+      </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A608" s="6"/>
       <c r="B608" s="4"/>
       <c r="C608" s="5"/>
-      <c r="D608"/>
+      <c r="D608" s="6" t="s">
+        <v>610</v>
+      </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A609" s="6"/>
       <c r="B609" s="4"/>
       <c r="C609" s="5"/>
-      <c r="D609"/>
+      <c r="D609" s="6" t="s">
+        <v>600</v>
+      </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A610" s="6"/>
       <c r="B610" s="4"/>
       <c r="C610" s="5"/>
-      <c r="D610"/>
+      <c r="D610" s="6" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A611" s="6"/>
       <c r="B611" s="4"/>
       <c r="C611" s="5"/>
-      <c r="D611"/>
+      <c r="D611" s="6" t="s">
+        <v>611</v>
+      </c>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A612" s="6"/>
       <c r="B612" s="4"/>
       <c r="C612" s="5"/>
-      <c r="D612"/>
+      <c r="D612" s="6" t="s">
+        <v>602</v>
+      </c>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A613" s="6"/>
       <c r="B613" s="4"/>
       <c r="C613" s="5"/>
-      <c r="D613"/>
+      <c r="D613" s="6" t="s">
+        <v>612</v>
+      </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B614" s="2"/>
-      <c r="D614"/>
+      <c r="D614" s="6" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A615" s="6"/>
       <c r="B615" s="6"/>
       <c r="C615" s="5"/>
-      <c r="D615"/>
+      <c r="D615" s="6" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A616" s="6"/>
       <c r="B616" s="4"/>
       <c r="C616" s="5"/>
-      <c r="D616"/>
+      <c r="D616" s="6" t="s">
+        <v>614</v>
+      </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A617" s="6"/>

--- a/memo/フリガナチェック.xlsx
+++ b/memo/フリガナチェック.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saisen-my.sharepoint.com/personal/ochi_saisen_ac_jp/Documents/ドキュメント/MyDocs/JavaScript_new/memo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="8_{523B395E-461C-49F3-9826-BD1CEC3361E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C0FB26D-5484-43DE-BAEB-976349BEBBAA}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="8_{523B395E-461C-49F3-9826-BD1CEC3361E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55489286-312B-4600-AE09-968FD90451D2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8071D02F-48A5-4AAB-9F2F-C41812D8E7C4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="692">
   <si>
     <t>－－</t>
   </si>
@@ -2012,6 +2012,249 @@
   </si>
   <si>
     <t>取り除く</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>プリミティブ</t>
+  </si>
+  <si>
+    <t>うい</t>
+  </si>
+  <si>
+    <t>ラッパーオブジェクト</t>
+  </si>
+  <si>
+    <t>ラッパー</t>
+  </si>
+  <si>
+    <t>ラッピング</t>
+  </si>
+  <si>
+    <t>定着</t>
+  </si>
+  <si>
+    <t>身軽</t>
+  </si>
+  <si>
+    <t>シール</t>
+  </si>
+  <si>
+    <t>リ</t>
+  </si>
+  <si>
+    <t>プレ</t>
+  </si>
+  <si>
+    <t>イス</t>
+  </si>
+  <si>
+    <t>入</t>
+  </si>
+  <si>
+    <t>スプリット</t>
+  </si>
+  <si>
+    <t>カンマ</t>
+  </si>
+  <si>
+    <t>韓国</t>
+  </si>
+  <si>
+    <t>中国</t>
+  </si>
+  <si>
+    <t>トリム</t>
+  </si>
+  <si>
+    <t>空白</t>
+  </si>
+  <si>
+    <t>トリミング</t>
+  </si>
+  <si>
+    <t>パキパキ</t>
+  </si>
+  <si>
+    <t>スキマ</t>
+  </si>
+  <si>
+    <t>ムダ</t>
+  </si>
+  <si>
+    <t>N1 32 (16)</t>
+  </si>
+  <si>
+    <t>分裂</t>
+  </si>
+  <si>
+    <t>名簿</t>
+  </si>
+  <si>
+    <t>カット</t>
+  </si>
+  <si>
+    <t>変身</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>切</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>切り抜き</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>置き換える</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>替る</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>づく</t>
+  </si>
+  <si>
+    <t>指し示す</t>
+  </si>
+  <si>
+    <t>りん</t>
+  </si>
+  <si>
+    <t>劇的</t>
+  </si>
+  <si>
+    <t>速める</t>
+  </si>
+  <si>
+    <t>取り出し</t>
+  </si>
+  <si>
+    <t>泣かせる</t>
+  </si>
+  <si>
+    <t>かっこいい</t>
+  </si>
+  <si>
+    <t>合言葉</t>
+  </si>
+  <si>
+    <t>火水</t>
+  </si>
+  <si>
+    <t>クリア</t>
+  </si>
+  <si>
+    <t>頼り</t>
+  </si>
+  <si>
+    <t>ゲット</t>
+  </si>
+  <si>
+    <t>繰る</t>
+  </si>
+  <si>
+    <t>算</t>
+  </si>
+  <si>
+    <t>引</t>
+  </si>
+  <si>
+    <t>変換</t>
+  </si>
+  <si>
+    <t>マス</t>
+  </si>
+  <si>
+    <t>小数点</t>
+  </si>
+  <si>
+    <t>切り上げる</t>
+  </si>
+  <si>
+    <t>N1 22 (13)</t>
+  </si>
+  <si>
+    <t>参照</t>
+  </si>
+  <si>
+    <t>策</t>
+  </si>
+  <si>
+    <t>めくる</t>
+  </si>
+  <si>
+    <t>実体</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サイコロ</t>
+  </si>
+  <si>
+    <t>乱数</t>
+  </si>
+  <si>
+    <t>ダメージ</t>
+  </si>
+  <si>
+    <t>ラッキー</t>
+  </si>
+  <si>
+    <t>ガラガラ</t>
+  </si>
+  <si>
+    <t>しす</t>
+  </si>
+  <si>
+    <t>切り捨てる</t>
+  </si>
+  <si>
+    <t>きんてん</t>
+  </si>
+  <si>
+    <t>切り捨て</t>
+  </si>
+  <si>
+    <t>ランダム</t>
+  </si>
+  <si>
+    <t>せいす</t>
+  </si>
+  <si>
+    <t>ワンポイント</t>
+  </si>
+  <si>
+    <t>N1 17 (14)</t>
+  </si>
+  <si>
+    <t>ちゅうせん</t>
+  </si>
+  <si>
+    <t>ダウン</t>
+  </si>
+  <si>
+    <t>切り上げ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>天才</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>使い道</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>抽選</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>当て</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>挑戦</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -7044,453 +7287,607 @@
       <c r="A617" s="6"/>
       <c r="B617" s="4"/>
       <c r="C617" s="5"/>
-      <c r="D617"/>
+      <c r="D617" s="6" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A618" s="6"/>
       <c r="B618" s="6"/>
       <c r="C618" s="5"/>
-      <c r="D618"/>
+      <c r="D618" s="6" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A619" s="6"/>
       <c r="B619" s="6"/>
       <c r="C619" s="5"/>
-      <c r="D619"/>
+      <c r="D619" s="6" t="s">
+        <v>617</v>
+      </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A620" s="6"/>
       <c r="B620" s="4"/>
       <c r="C620" s="5"/>
-      <c r="D620"/>
+      <c r="D620" s="6" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A621" s="6"/>
       <c r="B621" s="4"/>
       <c r="C621" s="5"/>
-      <c r="D621"/>
+      <c r="D621" s="6" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A622" s="6"/>
       <c r="B622" s="4"/>
       <c r="C622" s="5"/>
-      <c r="D622"/>
+      <c r="D622" s="6" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A623" s="6"/>
       <c r="B623" s="4"/>
       <c r="C623" s="5"/>
-      <c r="D623"/>
+      <c r="D623" s="6" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A624" s="6"/>
       <c r="B624" s="6"/>
       <c r="C624" s="5"/>
-      <c r="D624"/>
+      <c r="D624" s="6" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A625" s="6"/>
       <c r="B625" s="4"/>
       <c r="C625" s="5"/>
-      <c r="D625"/>
+      <c r="D625" s="6" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A626" s="6"/>
       <c r="B626" s="4"/>
       <c r="C626" s="5"/>
-      <c r="D626"/>
+      <c r="D626" s="6" t="s">
+        <v>642</v>
+      </c>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A627" s="6"/>
       <c r="B627" s="4"/>
       <c r="C627" s="5"/>
-      <c r="D627"/>
+      <c r="D627" s="6" t="s">
+        <v>643</v>
+      </c>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A628" s="6"/>
       <c r="B628" s="4"/>
       <c r="C628" s="5"/>
-      <c r="D628"/>
+      <c r="D628" s="6" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A629" s="6"/>
       <c r="B629" s="4"/>
       <c r="C629" s="5"/>
-      <c r="D629"/>
+      <c r="D629" s="6" t="s">
+        <v>624</v>
+      </c>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A630" s="6"/>
       <c r="B630" s="4"/>
       <c r="C630" s="5"/>
-      <c r="D630"/>
+      <c r="D630" s="6" t="s">
+        <v>625</v>
+      </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A631" s="6"/>
       <c r="B631" s="4"/>
       <c r="C631" s="5"/>
-      <c r="D631"/>
+      <c r="D631" s="6" t="s">
+        <v>644</v>
+      </c>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A632" s="6"/>
       <c r="B632" s="4"/>
       <c r="C632" s="5"/>
-      <c r="D632"/>
+      <c r="D632" s="6" t="s">
+        <v>626</v>
+      </c>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A633" s="6"/>
       <c r="B633" s="4"/>
       <c r="C633" s="5"/>
-      <c r="D633"/>
+      <c r="D633" s="6" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A634" s="6"/>
       <c r="B634" s="4"/>
       <c r="C634" s="5"/>
-      <c r="D634"/>
+      <c r="D634" s="6" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A635" s="6"/>
       <c r="B635" s="4"/>
       <c r="C635" s="5"/>
-      <c r="D635"/>
+      <c r="D635" s="6" t="s">
+        <v>628</v>
+      </c>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A636" s="6"/>
       <c r="B636" s="4"/>
       <c r="C636" s="5"/>
-      <c r="D636"/>
+      <c r="D636" s="6" t="s">
+        <v>629</v>
+      </c>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A637" s="6"/>
       <c r="B637" s="4"/>
       <c r="C637" s="5"/>
-      <c r="D637"/>
+      <c r="D637" s="6" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A638" s="6"/>
       <c r="B638" s="4"/>
       <c r="C638" s="5"/>
-      <c r="D638"/>
+      <c r="D638" s="6" t="s">
+        <v>631</v>
+      </c>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B639" s="2"/>
-      <c r="D639"/>
+      <c r="D639" s="6" t="s">
+        <v>632</v>
+      </c>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A640" s="6"/>
       <c r="B640" s="4"/>
       <c r="C640" s="5"/>
-      <c r="D640"/>
+      <c r="D640" s="6" t="s">
+        <v>633</v>
+      </c>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A641" s="6"/>
       <c r="B641" s="6"/>
       <c r="C641" s="5"/>
-      <c r="D641"/>
+      <c r="D641" s="6" t="s">
+        <v>634</v>
+      </c>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A642" s="6"/>
       <c r="B642" s="4"/>
       <c r="C642" s="5"/>
-      <c r="D642"/>
+      <c r="D642" s="6" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A643" s="6"/>
       <c r="B643" s="4"/>
       <c r="C643" s="5"/>
-      <c r="D643"/>
+      <c r="D643" s="6" t="s">
+        <v>636</v>
+      </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A644" s="6"/>
       <c r="B644" s="4"/>
       <c r="C644" s="5"/>
-      <c r="D644"/>
+      <c r="D644" s="6" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A645" s="6"/>
       <c r="B645" s="4"/>
       <c r="C645" s="5"/>
-      <c r="D645"/>
+      <c r="D645" s="6" t="s">
+        <v>638</v>
+      </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B646" s="1"/>
-      <c r="D646"/>
+      <c r="D646" s="6" t="s">
+        <v>639</v>
+      </c>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A647" s="6"/>
       <c r="B647" s="4"/>
       <c r="C647" s="5"/>
-      <c r="D647"/>
+      <c r="D647" s="6" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A648" s="6"/>
       <c r="B648" s="4"/>
       <c r="C648" s="5"/>
-      <c r="D648"/>
+      <c r="D648" s="6" t="s">
+        <v>646</v>
+      </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A649" s="6"/>
       <c r="B649" s="4"/>
       <c r="C649" s="5"/>
-      <c r="D649"/>
+      <c r="D649" s="6" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A650" s="6"/>
       <c r="B650" s="4"/>
       <c r="C650" s="5"/>
-      <c r="D650"/>
+      <c r="D650" s="6" t="s">
+        <v>647</v>
+      </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A651" s="6"/>
       <c r="B651" s="4"/>
       <c r="C651" s="5"/>
-      <c r="D651"/>
+      <c r="D651" s="6" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A652" s="6"/>
       <c r="B652" s="4"/>
       <c r="C652" s="5"/>
-      <c r="D652"/>
+      <c r="D652" s="6" t="s">
+        <v>649</v>
+      </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A653" s="6"/>
       <c r="B653" s="4"/>
       <c r="C653" s="5"/>
-      <c r="D653"/>
+      <c r="D653" s="6" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A654" s="6"/>
       <c r="B654" s="4"/>
       <c r="C654" s="5"/>
-      <c r="D654"/>
+      <c r="D654" s="6" t="s">
+        <v>651</v>
+      </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A655" s="6"/>
       <c r="B655" s="4"/>
       <c r="C655" s="5"/>
-      <c r="D655"/>
+      <c r="D655" s="6" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A656" s="6"/>
       <c r="B656" s="4"/>
       <c r="C656" s="5"/>
-      <c r="D656"/>
+      <c r="D656" s="6" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A657" s="6"/>
       <c r="B657" s="4"/>
       <c r="C657" s="5"/>
-      <c r="D657"/>
+      <c r="D657" s="6" t="s">
+        <v>654</v>
+      </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A658" s="6"/>
       <c r="B658" s="4"/>
       <c r="C658" s="5"/>
-      <c r="D658"/>
+      <c r="D658" s="6" t="s">
+        <v>655</v>
+      </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A659" s="6"/>
       <c r="B659" s="4"/>
       <c r="C659" s="5"/>
-      <c r="D659"/>
+      <c r="D659" s="6" t="s">
+        <v>656</v>
+      </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A660" s="6"/>
       <c r="B660" s="4"/>
       <c r="C660" s="5"/>
-      <c r="D660"/>
+      <c r="D660" s="6" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A661" s="6"/>
       <c r="B661" s="4"/>
       <c r="C661" s="5"/>
-      <c r="D661"/>
+      <c r="D661" s="6" t="s">
+        <v>658</v>
+      </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A662" s="6"/>
       <c r="B662" s="4"/>
       <c r="C662" s="5"/>
-      <c r="D662"/>
+      <c r="D662" s="6" t="s">
+        <v>659</v>
+      </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A663" s="6"/>
       <c r="B663" s="4"/>
       <c r="C663" s="5"/>
-      <c r="D663"/>
+      <c r="D663" s="6" t="s">
+        <v>660</v>
+      </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A664" s="6"/>
       <c r="B664" s="4"/>
       <c r="C664" s="5"/>
-      <c r="D664"/>
+      <c r="D664" s="6" t="s">
+        <v>661</v>
+      </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A665" s="6"/>
       <c r="B665" s="4"/>
       <c r="C665" s="5"/>
-      <c r="D665"/>
+      <c r="D665" s="6" t="s">
+        <v>662</v>
+      </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A666" s="6"/>
       <c r="B666" s="4"/>
       <c r="C666" s="5"/>
-      <c r="D666"/>
+      <c r="D666" s="6" t="s">
+        <v>663</v>
+      </c>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A667" s="6"/>
       <c r="B667" s="4"/>
       <c r="C667" s="5"/>
-      <c r="D667"/>
+      <c r="D667" s="6" t="s">
+        <v>664</v>
+      </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B668" s="1"/>
-      <c r="D668"/>
+      <c r="D668" s="6" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A669" s="6"/>
       <c r="B669" s="4"/>
       <c r="C669" s="5"/>
-      <c r="D669"/>
+      <c r="D669" s="6" t="s">
+        <v>666</v>
+      </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A670" s="6"/>
       <c r="B670" s="4"/>
       <c r="C670" s="5"/>
-      <c r="D670"/>
+      <c r="D670" s="6" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A671" s="6"/>
       <c r="B671" s="4"/>
       <c r="C671" s="5"/>
-      <c r="D671"/>
+      <c r="D671" s="6" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B672" s="2"/>
-      <c r="D672"/>
+      <c r="D672" s="6" t="s">
+        <v>669</v>
+      </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A673" s="6"/>
       <c r="B673" s="6"/>
       <c r="C673" s="5"/>
-      <c r="D673"/>
+      <c r="D673" s="6" t="s">
+        <v>671</v>
+      </c>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A674" s="6"/>
       <c r="B674" s="4"/>
       <c r="C674" s="5"/>
-      <c r="D674"/>
+      <c r="D674" s="6" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A675" s="6"/>
       <c r="B675" s="4"/>
       <c r="C675" s="5"/>
-      <c r="D675"/>
+      <c r="D675" s="6" t="s">
+        <v>673</v>
+      </c>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A676" s="6"/>
       <c r="B676" s="4"/>
       <c r="C676" s="5"/>
-      <c r="D676"/>
+      <c r="D676" s="6" t="s">
+        <v>674</v>
+      </c>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A677" s="6"/>
       <c r="B677" s="6"/>
       <c r="C677" s="5"/>
-      <c r="D677"/>
+      <c r="D677" s="6" t="s">
+        <v>675</v>
+      </c>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A678" s="6"/>
       <c r="B678" s="4"/>
       <c r="C678" s="5"/>
-      <c r="D678"/>
+      <c r="D678" s="6" t="s">
+        <v>676</v>
+      </c>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A679" s="6"/>
       <c r="B679" s="6"/>
       <c r="C679" s="5"/>
-      <c r="D679"/>
+      <c r="D679" s="6" t="s">
+        <v>677</v>
+      </c>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A680" s="6"/>
       <c r="B680" s="4"/>
       <c r="C680" s="5"/>
-      <c r="D680"/>
+      <c r="D680" s="6" t="s">
+        <v>678</v>
+      </c>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A681" s="6"/>
       <c r="B681" s="4"/>
       <c r="C681" s="5"/>
-      <c r="D681"/>
+      <c r="D681" s="6" t="s">
+        <v>686</v>
+      </c>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A682" s="6"/>
       <c r="B682" s="4"/>
       <c r="C682" s="5"/>
-      <c r="D682"/>
+      <c r="D682" s="6" t="s">
+        <v>679</v>
+      </c>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A683" s="6"/>
       <c r="B683" s="4"/>
       <c r="C683" s="5"/>
-      <c r="D683"/>
+      <c r="D683" s="6" t="s">
+        <v>680</v>
+      </c>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A684" s="6"/>
       <c r="B684" s="4"/>
       <c r="C684" s="5"/>
-      <c r="D684"/>
+      <c r="D684" s="6" t="s">
+        <v>681</v>
+      </c>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A685" s="6"/>
       <c r="B685" s="4"/>
       <c r="C685" s="5"/>
-      <c r="D685"/>
+      <c r="D685" s="6" t="s">
+        <v>682</v>
+      </c>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B686" s="1"/>
-      <c r="D686"/>
+      <c r="D686" s="6" t="s">
+        <v>683</v>
+      </c>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A687" s="6"/>
       <c r="B687" s="4"/>
       <c r="C687" s="5"/>
-      <c r="D687"/>
+      <c r="D687" s="6" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A688" s="6"/>
       <c r="B688" s="4"/>
       <c r="C688" s="5"/>
-      <c r="D688"/>
+      <c r="D688" s="6" t="s">
+        <v>688</v>
+      </c>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A689" s="6"/>
       <c r="B689" s="4"/>
       <c r="C689" s="5"/>
-      <c r="D689"/>
+      <c r="D689" s="6" t="s">
+        <v>689</v>
+      </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A690" s="6"/>
       <c r="B690" s="4"/>
       <c r="C690" s="5"/>
-      <c r="D690"/>
+      <c r="D690" s="6" t="s">
+        <v>684</v>
+      </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A691" s="6"/>
       <c r="B691" s="4"/>
       <c r="C691" s="5"/>
-      <c r="D691"/>
+      <c r="D691" s="6" t="s">
+        <v>685</v>
+      </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A692" s="6"/>
       <c r="B692" s="4"/>
       <c r="C692" s="5"/>
-      <c r="D692"/>
+      <c r="D692" s="6" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A693" s="6"/>
       <c r="B693" s="4"/>
       <c r="C693" s="5"/>
-      <c r="D693"/>
+      <c r="D693" s="6" t="s">
+        <v>691</v>
+      </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A694" s="6"/>

--- a/memo/フリガナチェック.xlsx
+++ b/memo/フリガナチェック.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saisen-my.sharepoint.com/personal/ochi_saisen_ac_jp/Documents/ドキュメント/MyDocs/JavaScript_new/memo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{523B395E-461C-49F3-9826-BD1CEC3361E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55489286-312B-4600-AE09-968FD90451D2}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{523B395E-461C-49F3-9826-BD1CEC3361E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{074E02DA-23E9-4065-B042-A41856289625}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8071D02F-48A5-4AAB-9F2F-C41812D8E7C4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="692">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="762">
   <si>
     <t>－－</t>
   </si>
@@ -2256,6 +2256,223 @@
   <si>
     <t>挑戦</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>指向</t>
+  </si>
+  <si>
+    <t>いろんな</t>
+  </si>
+  <si>
+    <t>継承</t>
+  </si>
+  <si>
+    <t>ブラケット</t>
+  </si>
+  <si>
+    <t>といった</t>
+  </si>
+  <si>
+    <t>モノ</t>
+  </si>
+  <si>
+    <t>アリ</t>
+  </si>
+  <si>
+    <t>エジプト</t>
+  </si>
+  <si>
+    <t>記</t>
+  </si>
+  <si>
+    <t>芳</t>
+  </si>
+  <si>
+    <t>記法</t>
+  </si>
+  <si>
+    <t>つよ</t>
+  </si>
+  <si>
+    <t>ほぞ</t>
+  </si>
+  <si>
+    <t>プロジェクト</t>
+  </si>
+  <si>
+    <t>インスタンス</t>
+  </si>
+  <si>
+    <t>N1 43 (19)</t>
+  </si>
+  <si>
+    <t>振り返る</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>強</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>既存</t>
+  </si>
+  <si>
+    <t>カスタマイズ</t>
+  </si>
+  <si>
+    <t>ステッカー</t>
+  </si>
+  <si>
+    <t>プップー</t>
+  </si>
+  <si>
+    <t>ライ</t>
+  </si>
+  <si>
+    <t>ド</t>
+  </si>
+  <si>
+    <t>上書き</t>
+  </si>
+  <si>
+    <t>受</t>
+  </si>
+  <si>
+    <t>さいし</t>
+  </si>
+  <si>
+    <t>ハロー</t>
+  </si>
+  <si>
+    <t>ロボット</t>
+  </si>
+  <si>
+    <t>ラップ</t>
+  </si>
+  <si>
+    <t>着信</t>
+  </si>
+  <si>
+    <t>プロトタイプ</t>
+  </si>
+  <si>
+    <t>チェーン</t>
+  </si>
+  <si>
+    <t>山場</t>
+  </si>
+  <si>
+    <t>系図</t>
+  </si>
+  <si>
+    <t>レシピ</t>
+  </si>
+  <si>
+    <t>メモリー</t>
+  </si>
+  <si>
+    <t>ラウンジ</t>
+  </si>
+  <si>
+    <t>ブログラム</t>
+  </si>
+  <si>
+    <t>けいしょう</t>
+  </si>
+  <si>
+    <t>N1 30 (20)</t>
+  </si>
+  <si>
+    <t>スト</t>
+  </si>
+  <si>
+    <t>また</t>
+  </si>
+  <si>
+    <t>身近</t>
+  </si>
+  <si>
+    <t>継</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>やり方</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>譲り受ける</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>お気に入り</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>秘伝</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>コンス</t>
+  </si>
+  <si>
+    <t>トラクタ</t>
+  </si>
+  <si>
+    <t>手書き</t>
+  </si>
+  <si>
+    <t>焼き</t>
+  </si>
+  <si>
+    <t>自体</t>
+  </si>
+  <si>
+    <t>あんこ</t>
+  </si>
+  <si>
+    <t>リン</t>
+  </si>
+  <si>
+    <t>いぶ</t>
+  </si>
+  <si>
+    <t>ハンコ</t>
+  </si>
+  <si>
+    <t>スタンプ</t>
+  </si>
+  <si>
+    <t>ポ</t>
+  </si>
+  <si>
+    <t>ン</t>
+  </si>
+  <si>
+    <t>えて</t>
+  </si>
+  <si>
+    <t>イヌ</t>
+  </si>
+  <si>
+    <t>ネコ</t>
+  </si>
+  <si>
+    <t>イクステンズ</t>
+  </si>
+  <si>
+    <t>アハメド</t>
+  </si>
+  <si>
+    <t>N1 24 (13)</t>
+  </si>
+  <si>
+    <t>規模</t>
+  </si>
+  <si>
+    <t>個性</t>
+  </si>
+  <si>
+    <t>ベース</t>
   </si>
 </sst>
 </file>
@@ -7893,411 +8110,551 @@
       <c r="A694" s="6"/>
       <c r="B694" s="4"/>
       <c r="C694" s="5"/>
-      <c r="D694"/>
+      <c r="D694" s="6" t="s">
+        <v>692</v>
+      </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A695" s="6"/>
       <c r="B695" s="4"/>
       <c r="C695" s="5"/>
-      <c r="D695"/>
+      <c r="D695" s="6" t="s">
+        <v>693</v>
+      </c>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A696" s="6"/>
       <c r="B696" s="4"/>
       <c r="C696" s="5"/>
-      <c r="D696"/>
+      <c r="D696" s="6" t="s">
+        <v>694</v>
+      </c>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A697" s="6"/>
       <c r="B697" s="4"/>
       <c r="C697" s="5"/>
-      <c r="D697"/>
+      <c r="D697" s="6" t="s">
+        <v>695</v>
+      </c>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A698" s="6"/>
       <c r="B698" s="4"/>
       <c r="C698" s="5"/>
-      <c r="D698"/>
+      <c r="D698" s="6" t="s">
+        <v>696</v>
+      </c>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A699" s="6"/>
       <c r="B699" s="4"/>
       <c r="C699" s="5"/>
-      <c r="D699"/>
+      <c r="D699" s="6" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A700" s="6"/>
       <c r="B700" s="4"/>
       <c r="C700" s="5"/>
-      <c r="D700"/>
+      <c r="D700" s="6" t="s">
+        <v>698</v>
+      </c>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A701" s="6"/>
       <c r="B701" s="4"/>
       <c r="C701" s="5"/>
-      <c r="D701"/>
+      <c r="D701" s="6" t="s">
+        <v>699</v>
+      </c>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A702" s="6"/>
       <c r="B702" s="4"/>
       <c r="C702" s="5"/>
-      <c r="D702"/>
+      <c r="D702" s="6" t="s">
+        <v>700</v>
+      </c>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B703" s="1"/>
-      <c r="D703"/>
+      <c r="D703" s="6" t="s">
+        <v>701</v>
+      </c>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A704" s="6"/>
       <c r="B704" s="4"/>
       <c r="C704" s="5"/>
-      <c r="D704"/>
+      <c r="D704" s="6" t="s">
+        <v>702</v>
+      </c>
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A705" s="6"/>
       <c r="B705" s="4"/>
       <c r="C705" s="5"/>
-      <c r="D705"/>
+      <c r="D705" s="6" t="s">
+        <v>703</v>
+      </c>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A706" s="6"/>
       <c r="B706" s="6"/>
       <c r="C706" s="5"/>
-      <c r="D706"/>
+      <c r="D706" s="6" t="s">
+        <v>704</v>
+      </c>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A707" s="6"/>
       <c r="B707" s="4"/>
       <c r="C707" s="5"/>
-      <c r="D707"/>
+      <c r="D707" s="6" t="s">
+        <v>705</v>
+      </c>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A708" s="6"/>
       <c r="B708" s="6"/>
       <c r="C708" s="5"/>
-      <c r="D708"/>
+      <c r="D708" s="6" t="s">
+        <v>706</v>
+      </c>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A709" s="6"/>
       <c r="B709" s="6"/>
       <c r="C709" s="5"/>
-      <c r="D709"/>
+      <c r="D709" s="6" t="s">
+        <v>707</v>
+      </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A710" s="6"/>
       <c r="B710" s="4"/>
       <c r="C710" s="5"/>
-      <c r="D710"/>
+      <c r="D710" s="6" t="s">
+        <v>708</v>
+      </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A711" s="6"/>
       <c r="B711" s="4"/>
       <c r="C711" s="5"/>
-      <c r="D711"/>
+      <c r="D711" s="6" t="s">
+        <v>709</v>
+      </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A712" s="6"/>
       <c r="B712" s="4"/>
       <c r="C712" s="5"/>
-      <c r="D712"/>
+      <c r="D712" s="6" t="s">
+        <v>710</v>
+      </c>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A713" s="6"/>
       <c r="B713" s="4"/>
       <c r="C713" s="5"/>
-      <c r="D713"/>
+      <c r="D713" s="6" t="s">
+        <v>711</v>
+      </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A714" s="6"/>
       <c r="B714" s="4"/>
       <c r="C714" s="5"/>
-      <c r="D714"/>
+      <c r="D714" s="6" t="s">
+        <v>712</v>
+      </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A715" s="6"/>
       <c r="B715" s="4"/>
       <c r="C715" s="5"/>
-      <c r="D715"/>
+      <c r="D715" s="6" t="s">
+        <v>713</v>
+      </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A716" s="6"/>
       <c r="B716" s="6"/>
       <c r="C716" s="5"/>
-      <c r="D716"/>
+      <c r="D716" s="6" t="s">
+        <v>714</v>
+      </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A717" s="6"/>
       <c r="B717" s="4"/>
       <c r="C717" s="5"/>
-      <c r="D717"/>
+      <c r="D717" s="6" t="s">
+        <v>715</v>
+      </c>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A718" s="6"/>
       <c r="B718" s="4"/>
       <c r="C718" s="5"/>
-      <c r="D718"/>
+      <c r="D718" s="6" t="s">
+        <v>716</v>
+      </c>
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A719" s="6"/>
       <c r="B719" s="4"/>
       <c r="C719" s="5"/>
-      <c r="D719"/>
+      <c r="D719" s="6" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A720" s="6"/>
       <c r="B720" s="4"/>
       <c r="C720" s="5"/>
-      <c r="D720"/>
+      <c r="D720" s="6" t="s">
+        <v>736</v>
+      </c>
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A721" s="6"/>
       <c r="B721" s="4"/>
       <c r="C721" s="5"/>
-      <c r="D721"/>
+      <c r="D721" s="6" t="s">
+        <v>737</v>
+      </c>
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A722" s="6"/>
       <c r="B722" s="6"/>
       <c r="C722" s="5"/>
-      <c r="D722"/>
+      <c r="D722" s="6" t="s">
+        <v>738</v>
+      </c>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A723" s="6"/>
       <c r="B723" s="6"/>
       <c r="C723" s="5"/>
-      <c r="D723"/>
+      <c r="D723" s="6" t="s">
+        <v>718</v>
+      </c>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A724" s="6"/>
       <c r="B724" s="4"/>
       <c r="C724" s="5"/>
-      <c r="D724"/>
+      <c r="D724" s="6" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B725" s="1"/>
-      <c r="D725"/>
+      <c r="D725" s="6" t="s">
+        <v>720</v>
+      </c>
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A726" s="6"/>
       <c r="B726" s="6"/>
       <c r="C726" s="5"/>
-      <c r="D726"/>
+      <c r="D726" s="6" t="s">
+        <v>739</v>
+      </c>
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A727" s="6"/>
       <c r="B727" s="6"/>
       <c r="C727" s="5"/>
-      <c r="D727"/>
+      <c r="D727" s="6" t="s">
+        <v>721</v>
+      </c>
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A728" s="6"/>
       <c r="B728" s="4"/>
       <c r="C728" s="5"/>
-      <c r="D728"/>
+      <c r="D728" s="6" t="s">
+        <v>722</v>
+      </c>
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A729" s="6"/>
       <c r="B729" s="4"/>
       <c r="C729" s="5"/>
-      <c r="D729"/>
+      <c r="D729" s="6" t="s">
+        <v>723</v>
+      </c>
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A730" s="6"/>
       <c r="B730" s="4"/>
       <c r="C730" s="5"/>
-      <c r="D730"/>
+      <c r="D730" s="6" t="s">
+        <v>724</v>
+      </c>
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A731" s="6"/>
       <c r="B731" s="4"/>
       <c r="C731" s="5"/>
-      <c r="D731"/>
+      <c r="D731" s="6" t="s">
+        <v>725</v>
+      </c>
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A732" s="6"/>
       <c r="B732" s="4"/>
       <c r="C732" s="5"/>
-      <c r="D732"/>
+      <c r="D732" s="6" t="s">
+        <v>726</v>
+      </c>
     </row>
     <row r="733" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A733" s="6"/>
       <c r="B733" s="4"/>
       <c r="C733" s="5"/>
-      <c r="D733"/>
+      <c r="D733" s="6" t="s">
+        <v>740</v>
+      </c>
     </row>
     <row r="734" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A734" s="6"/>
       <c r="B734" s="4"/>
       <c r="C734" s="5"/>
-      <c r="D734"/>
+      <c r="D734" s="6" t="s">
+        <v>727</v>
+      </c>
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A735" s="6"/>
       <c r="B735" s="4"/>
       <c r="C735" s="5"/>
-      <c r="D735"/>
+      <c r="D735" s="6" t="s">
+        <v>728</v>
+      </c>
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B736" s="2"/>
-      <c r="D736"/>
+      <c r="D736" s="6" t="s">
+        <v>729</v>
+      </c>
     </row>
     <row r="737" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A737" s="6"/>
       <c r="B737" s="4"/>
       <c r="C737" s="5"/>
-      <c r="D737"/>
+      <c r="D737" s="6" t="s">
+        <v>730</v>
+      </c>
     </row>
     <row r="738" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A738" s="6"/>
       <c r="B738" s="4"/>
       <c r="C738" s="5"/>
-      <c r="D738"/>
+      <c r="D738" s="6" t="s">
+        <v>731</v>
+      </c>
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A739" s="6"/>
       <c r="B739" s="4"/>
       <c r="C739" s="5"/>
-      <c r="D739"/>
+      <c r="D739" s="6" t="s">
+        <v>732</v>
+      </c>
     </row>
     <row r="740" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A740" s="6"/>
       <c r="B740" s="4"/>
       <c r="C740" s="5"/>
-      <c r="D740"/>
+      <c r="D740" s="6" t="s">
+        <v>733</v>
+      </c>
     </row>
     <row r="741" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A741" s="6"/>
       <c r="B741" s="4"/>
       <c r="C741" s="5"/>
-      <c r="D741"/>
+      <c r="D741" s="6" t="s">
+        <v>734</v>
+      </c>
     </row>
     <row r="742" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B742" s="2"/>
-      <c r="D742"/>
+      <c r="D742" s="6" t="s">
+        <v>735</v>
+      </c>
     </row>
     <row r="743" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A743" s="6"/>
       <c r="B743" s="4"/>
       <c r="C743" s="5"/>
-      <c r="D743"/>
+      <c r="D743" s="6" t="s">
+        <v>741</v>
+      </c>
     </row>
     <row r="744" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A744" s="6"/>
       <c r="B744" s="4"/>
       <c r="C744" s="5"/>
-      <c r="D744"/>
+      <c r="D744" s="6" t="s">
+        <v>742</v>
+      </c>
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A745" s="6"/>
       <c r="B745" s="4"/>
       <c r="C745" s="5"/>
-      <c r="D745"/>
+      <c r="D745" s="6" t="s">
+        <v>743</v>
+      </c>
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B746" s="1"/>
-      <c r="D746"/>
+      <c r="D746" s="6" t="s">
+        <v>744</v>
+      </c>
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A747" s="6"/>
       <c r="B747" s="4"/>
       <c r="C747" s="5"/>
-      <c r="D747"/>
+      <c r="D747" s="6" t="s">
+        <v>745</v>
+      </c>
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A748" s="6"/>
       <c r="B748" s="4"/>
       <c r="C748" s="5"/>
-      <c r="D748"/>
+      <c r="D748" s="6" t="s">
+        <v>746</v>
+      </c>
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A749" s="6"/>
       <c r="B749" s="4"/>
       <c r="C749" s="5"/>
-      <c r="D749"/>
+      <c r="D749" s="6" t="s">
+        <v>747</v>
+      </c>
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A750" s="6"/>
       <c r="B750" s="6"/>
       <c r="C750" s="5"/>
-      <c r="D750"/>
+      <c r="D750" s="6" t="s">
+        <v>748</v>
+      </c>
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A751" s="6"/>
       <c r="B751" s="4"/>
       <c r="C751" s="5"/>
-      <c r="D751"/>
+      <c r="D751" s="6" t="s">
+        <v>749</v>
+      </c>
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A752" s="6"/>
       <c r="B752" s="4"/>
       <c r="C752" s="5"/>
-      <c r="D752"/>
+      <c r="D752" s="6" t="s">
+        <v>750</v>
+      </c>
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A753" s="6"/>
       <c r="B753" s="4"/>
       <c r="C753" s="5"/>
-      <c r="D753"/>
+      <c r="D753" s="6" t="s">
+        <v>751</v>
+      </c>
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A754" s="6"/>
       <c r="B754" s="4"/>
       <c r="C754" s="5"/>
-      <c r="D754"/>
+      <c r="D754" s="6" t="s">
+        <v>752</v>
+      </c>
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A755" s="6"/>
       <c r="B755" s="4"/>
       <c r="C755" s="5"/>
-      <c r="D755"/>
+      <c r="D755" s="6" t="s">
+        <v>753</v>
+      </c>
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A756" s="6"/>
       <c r="B756" s="4"/>
       <c r="C756" s="5"/>
-      <c r="D756"/>
+      <c r="D756" s="6" t="s">
+        <v>754</v>
+      </c>
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A757" s="6"/>
       <c r="B757" s="6"/>
       <c r="C757" s="5"/>
-      <c r="D757"/>
+      <c r="D757" s="6" t="s">
+        <v>755</v>
+      </c>
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A758" s="6"/>
       <c r="B758" s="4"/>
       <c r="C758" s="5"/>
-      <c r="D758"/>
+      <c r="D758" s="6" t="s">
+        <v>756</v>
+      </c>
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A759" s="6"/>
       <c r="B759" s="4"/>
       <c r="C759" s="5"/>
-      <c r="D759"/>
+      <c r="D759" s="6" t="s">
+        <v>757</v>
+      </c>
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A760" s="6"/>
       <c r="B760" s="4"/>
       <c r="C760" s="5"/>
-      <c r="D760"/>
+      <c r="D760" s="6" t="s">
+        <v>758</v>
+      </c>
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A761" s="6"/>
       <c r="B761" s="4"/>
       <c r="C761" s="5"/>
-      <c r="D761"/>
+      <c r="D761" s="6" t="s">
+        <v>759</v>
+      </c>
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A762" s="6"/>
       <c r="B762" s="4"/>
       <c r="C762" s="5"/>
-      <c r="D762"/>
+      <c r="D762" s="6" t="s">
+        <v>760</v>
+      </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A763" s="6"/>
       <c r="B763" s="4"/>
       <c r="C763" s="5"/>
-      <c r="D763"/>
+      <c r="D763" s="6" t="s">
+        <v>761</v>
+      </c>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A764" s="6"/>
@@ -11335,5 +11692,6 @@
   </sortState>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>